--- a/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/05_이슈보고/프로젝트명_Checklist_V1.0_20230530.xlsx
+++ b/public/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/05_이슈보고/프로젝트명_Checklist_V1.0_20230530.xlsx
@@ -520,7 +520,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-23] SyncGuard AI 단계별 품질·보안·인프라 핵심 점검 체크리스트 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-23] SyncFlow AI 단계별 품질·보안·인프라 핵심 점검 체크리스트 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>핵심 점검 항목 (SyncGuard AI 기준)</t>
+          <t>핵심 점검 항목 (SyncFlow AI 기준)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ProductLab 전성분 뷰 컬럼 매핑 및 일배치 시간(02:00) 합의 여부</t>
+          <t>PLM-Nexus 자재BOM 뷰 컬럼 매핑 및 일배치 시간(02:00) 합의 여부</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>ProductLab 원료 배합비 수치가 외부 상용 LLM 프롬프트에 평문 노출되지 않도록 격리되었는가</t>
+          <t>PLM-Nexus 원소재 조성비 수치가 외부 상용 LLM 프롬프트에 평문 노출되지 않도록 격리되었는가</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>골든셋 58문항 기준 정밀도(Precision) 95% 이상 및 단건 심의 15초 이내 달성 여부</t>
+          <t>골든셋 58문항 기준 정밀도(Precision) 95% 이상 및 단건 검증 15초 이내 달성 여부</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
